--- a/data/trans_orig/LAWTONBRODY_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/LAWTONBRODY_2023-Edad-trans_orig.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>7,55</t>
+          <t>7,57</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>7,61</t>
+          <t>7,36</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7,59</t>
+          <t>7,46</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,42; 7,65</t>
+          <t>7,45; 7,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,34; 7,85</t>
+          <t>7,21; 7,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,43; 7,79</t>
+          <t>7,37; 7,53</t>
         </is>
       </c>
     </row>
@@ -598,17 +598,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6,28</t>
+          <t>6,34</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5,25</t>
+          <t>5,27</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5,66</t>
+          <t>5,7</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,99; 6,5</t>
+          <t>6,09; 6,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,04; 5,44</t>
+          <t>5,08; 5,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,5; 5,81</t>
+          <t>5,53; 5,85</t>
         </is>
       </c>
     </row>
@@ -648,17 +648,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>6,96</t>
+          <t>7,0</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6,58</t>
+          <t>6,21</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6,73</t>
+          <t>6,56</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,82; 7,1</t>
+          <t>6,86; 7,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,17; 7,35</t>
+          <t>6,08; 6,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,51; 7,29</t>
+          <t>6,46; 6,65</t>
         </is>
       </c>
     </row>
